--- a/AAII_Financials/Yearly/ITOCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ITOCY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>ITOCY</t>
   </si>
@@ -656,150 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>93224000</v>
+      </c>
+      <c r="E8" s="3">
         <v>98326700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>92756700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>104906400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>101234800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>93695500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>102070300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>104688100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51881400</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>77623700</v>
+      </c>
+      <c r="E9" s="3">
         <v>82457000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>77997800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>88884200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>85282400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>77594600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>85362500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>90575900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>40484100</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15600300</v>
+      </c>
+      <c r="E10" s="3">
         <v>15869700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14758900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16022300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15952400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16100900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16707800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14112200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11397200</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -812,8 +824,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -841,9 +854,12 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -871,69 +887,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1021200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-453000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-187600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-128200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1599600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1387200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-496300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1720600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>212300</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1190100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1221900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1112000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1215700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1265600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1401600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3742700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1251800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>964300</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -943,68 +968,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>88809800</v>
+      </c>
+      <c r="E17" s="3">
         <v>93755800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>88107100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>99626300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>96437800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>90048000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>98358100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>101422800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>48897200</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4414300</v>
+      </c>
+      <c r="E18" s="3">
         <v>4571000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4649600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5280200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4797000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3647500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3712200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3265300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2984200</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1017,158 +1049,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2090000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2523100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2178400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2525600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2479400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2011200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-981700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2033300</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7694400</v>
+      </c>
+      <c r="E21" s="3">
         <v>8316000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7940000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9021500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8542000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7060400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9354900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5498800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5981800</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>664200</v>
+      </c>
+      <c r="E22" s="3">
         <v>697400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>665400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>503000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>238600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>327500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>535300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>490800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>390300</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7543600</v>
+      </c>
+      <c r="E23" s="3">
         <v>7713400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7244100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8326400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9470400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4633600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6518700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6275500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5064300</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1647800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1482800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1611700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1972300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2232100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>647300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1321700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1350900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>999400</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1196,69 +1244,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5895800</v>
+      </c>
+      <c r="E26" s="3">
         <v>6230600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5632400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6354100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7238300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3986300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5197000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4924500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4065000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5662000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5878200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5300800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6021900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6754900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3629600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4659000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4516900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3769400</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1286,9 +1343,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1316,9 +1376,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1346,9 +1409,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1376,69 +1442,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2090000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2523100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2178400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2525600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2479400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2011200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>981700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2033300</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5662000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5878200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5300800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6021900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6754900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3629600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4659000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4516900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3769400</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1466,74 +1541,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5662000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5878200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5300800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6021900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6754900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3629600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4659000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4516900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3769400</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1546,8 +1630,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1560,278 +1645,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3734300</v>
+      </c>
+      <c r="E41" s="3">
         <v>3670000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3969700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4558700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5037400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4918800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5680400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5162300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4068900</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1306200</v>
+      </c>
+      <c r="E42" s="3">
         <v>583200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>586000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>622900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>931500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>496200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>503500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>434800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>576700</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20257200</v>
+      </c>
+      <c r="E43" s="3">
         <v>20152600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20003100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20325100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21506600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20283100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21286200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23162000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21350200</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9715400</v>
+      </c>
+      <c r="E44" s="3">
         <v>9898900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9138000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9816500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8870300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8125700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8847700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8457600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8195000</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4420200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3918200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3483900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3202500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3263800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4850400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2092900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2561600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2750600</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39433300</v>
+      </c>
+      <c r="E46" s="3">
         <v>38222900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37180600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38525600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39609600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38674000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38410600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39778200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36941400</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34608200</v>
+      </c>
+      <c r="E47" s="3">
         <v>31498300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28776700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28375900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26738600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>25498900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>22832300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>21808000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>25058900</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15200100</v>
+      </c>
+      <c r="E48" s="3">
         <v>14901000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13954000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15033700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15943200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17539000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19864600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9727200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7657800</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7725700</v>
+      </c>
+      <c r="E49" s="3">
         <v>8076200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7459600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8118700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8907000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10179400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10809300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10177400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3413900</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1859,9 +1972,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1889,39 +2005,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1991100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1949600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2038600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2183900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2611600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2750800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2949900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3481700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2136000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1949,39 +2071,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105234500</v>
+      </c>
+      <c r="E54" s="3">
         <v>101064900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95796500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>98661000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>100084500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>101071700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>101481400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>91135300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>81577500</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1994,8 +2122,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2008,188 +2137,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15107600</v>
+      </c>
+      <c r="E57" s="3">
         <v>15108400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15491100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15365600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16199100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14726800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15868400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17525800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17191800</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6221400</v>
+      </c>
+      <c r="E58" s="3">
         <v>7094900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6294400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6755200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6244000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8577500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8610300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6257100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5090500</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8632900</v>
+      </c>
+      <c r="E59" s="3">
         <v>7757600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6923500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7554300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7618900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8835600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7136600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6371100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5860400</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29961900</v>
+      </c>
+      <c r="E60" s="3">
         <v>29960900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28709000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29675100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30062000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32139800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31615200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30154100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28142800</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23702600</v>
+      </c>
+      <c r="E61" s="3">
         <v>23768300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22770400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23419200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26011100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29568700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>29087800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22370000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21824200</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2510800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1798500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1568100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1654400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1859500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1956500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1981100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1917600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1368200</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2217,9 +2365,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2247,9 +2398,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2277,39 +2431,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60026800</v>
+      </c>
+      <c r="E66" s="3">
         <v>59056200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>56180500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57532500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60855800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66078300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>65788600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57834000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53477600</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2322,8 +2482,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2351,9 +2512,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2381,9 +2545,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2411,9 +2578,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2441,39 +2611,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>39431300</v>
+      </c>
+      <c r="E72" s="3">
         <v>37785400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>33268600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>33358400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>31391500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29285500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27398500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23538000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21889400</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2501,9 +2677,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2531,9 +2710,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2561,39 +2743,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41445000</v>
+      </c>
+      <c r="E76" s="3">
         <v>38431700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35879600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>36283100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>34581100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29984700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27842900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26504000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25135200</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2621,74 +2809,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5662000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5878200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5300800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6021900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6754900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3629600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4659000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4516900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3769400</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2701,38 +2898,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2513700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2620500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2434400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2710200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2933500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3403100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3384200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1067300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>868600</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2760,9 +2961,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2790,9 +2994,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2820,9 +3027,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2850,9 +3060,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2880,39 +3093,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7118200</v>
+      </c>
+      <c r="E89" s="3">
         <v>6659700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6466600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7056600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6597500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8100400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8160900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4300600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3655300</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2925,38 +3144,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1792300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1519000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1339100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1460000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1294100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1492100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1854300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1024900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1015300</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2984,9 +3207,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3014,39 +3240,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2445700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3447600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1361900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3413800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>318200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1874300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2311900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1815300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2413700</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3059,38 +3291,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1777900</v>
+      </c>
+      <c r="E96" s="3">
         <v>1727000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1490600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1417000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1114600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1166400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1241000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1050800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>874200</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3118,9 +3354,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3148,9 +3387,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3178,97 +3420,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4568900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3505900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5296800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3761900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6972600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6589300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5348200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4858000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2788300</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>174200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-45900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>155300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>76100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>249400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>156200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-136500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-86400</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>277900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-339700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-43000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>192500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-206900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>364200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1262400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1633200</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
